--- a/data/trans_dic/P44A$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 57,2</t>
+          <t>9,58; 58,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 52,11</t>
+          <t>15,34; 52,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 66,01</t>
+          <t>8,27; 63,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 79,88</t>
+          <t>18,36; 80,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 51,52</t>
+          <t>14,78; 51,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 53,53</t>
+          <t>21,48; 54,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 50,28</t>
+          <t>6,49; 54,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 49,14</t>
+          <t>11,19; 50,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,11; 100,0</t>
+          <t>28,91; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,58; 64,65</t>
+          <t>21,78; 63,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 48,97</t>
+          <t>14,12; 47,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,18</t>
+          <t>0,0; 24,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 38,12</t>
+          <t>6,27; 37,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,92; 83,53</t>
+          <t>18,47; 83,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 86,43</t>
+          <t>13,82; 86,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 36,42</t>
+          <t>8,71; 38,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 42,61</t>
+          <t>13,06; 43,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 26,78</t>
+          <t>2,95; 25,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 35,75</t>
+          <t>11,33; 34,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 50,05</t>
+          <t>6,78; 49,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 39,43</t>
+          <t>4,46; 41,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 26,76</t>
+          <t>6,1; 26,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,51; 31,0</t>
+          <t>12,21; 31,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,69</t>
+          <t>0,0; 63,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 29,63</t>
+          <t>3,9; 29,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 37,25</t>
+          <t>4,99; 41,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 37,51</t>
+          <t>6,63; 41,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,17</t>
+          <t>0,53; 4,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 37,57</t>
+          <t>6,81; 36,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 29,58</t>
+          <t>7,44; 28,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,74</t>
+          <t>0,61; 3,67</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,95; 58,9</t>
+          <t>22,42; 60,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 40,14</t>
+          <t>13,24; 41,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,95; 58,9</t>
+          <t>22,42; 60,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 40,14</t>
+          <t>13,24; 41,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 24,91</t>
+          <t>9,85; 25,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 30,06</t>
+          <t>16,52; 30,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,07</t>
+          <t>0,08; 1,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,98; 44,84</t>
+          <t>25,2; 44,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,27; 36,16</t>
+          <t>18,03; 35,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,17</t>
+          <t>0,13; 1,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,65; 32,16</t>
+          <t>19,71; 31,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,23; 30,47</t>
+          <t>18,8; 29,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,9</t>
+          <t>0,18; 0,91</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1832; 10957</t>
+          <t>1835; 11250</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4682; 16120</t>
+          <t>4746; 16150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1465</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1187; 8829</t>
+          <t>1105; 8544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1134; 8858</t>
+          <t>2036; 8896</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5212; 16761</t>
+          <t>4807; 16767</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8892; 22496</t>
+          <t>9025; 22948</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1284</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1096; 8160</t>
+          <t>1053; 8806</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2974; 13243</t>
+          <t>3014; 13739</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1511</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2917; 8308</t>
+          <t>2402; 8308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5295; 15863</t>
+          <t>5345; 15527</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4628; 15798</t>
+          <t>4556; 15275</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1297</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6497</t>
+          <t>0; 7029</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1929; 11132</t>
+          <t>1832; 10904</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8687</t>
+          <t>0; 10324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1953; 9106</t>
+          <t>2014; 9060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1062; 6356</t>
+          <t>1016; 6350</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1039</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3647; 14638</t>
+          <t>3501; 15397</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4091; 15577</t>
+          <t>4773; 16029</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 8048</t>
+          <t>0; 7727</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1060; 9702</t>
+          <t>1068; 9227</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5814; 17645</t>
+          <t>5594; 17198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3594</t>
+          <t>0; 3830</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>964; 7250</t>
+          <t>982; 7221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1110; 9584</t>
+          <t>1084; 10002</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1006</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3171; 13571</t>
+          <t>3093; 13608</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9212; 22837</t>
+          <t>8992; 23254</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3913</t>
+          <t>0; 3340</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5394</t>
+          <t>0; 5353</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>909; 6887</t>
+          <t>906; 6958</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1193; 10031</t>
+          <t>1344; 11302</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1149; 10282</t>
+          <t>1818; 11241</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>749; 5727</t>
+          <t>592; 5140</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3256; 13301</t>
+          <t>2411; 12863</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3537; 14985</t>
+          <t>3771; 14600</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>987; 6641</t>
+          <t>1083; 6506</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1027</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7334; 18824</t>
+          <t>7167; 19256</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4843; 15831</t>
+          <t>5222; 16354</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1017</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7334; 18824</t>
+          <t>7167; 19256</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4843; 15831</t>
+          <t>5222; 16354</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1023</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10251; 27241</t>
+          <t>10773; 27710</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26601; 47997</t>
+          <t>26384; 47921</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480; 8277</t>
+          <t>633; 8422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27529; 47508</t>
+          <t>26699; 47104</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20999; 41551</t>
+          <t>20717; 40909</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>594; 5536</t>
+          <t>599; 5226</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42309; 69247</t>
+          <t>42433; 68700</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>52793; 83682</t>
+          <t>51618; 82170</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2245; 11124</t>
+          <t>2251; 11255</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Clase-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 58,73</t>
+          <t>10,36; 59,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 52,2</t>
+          <t>16,07; 54,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 63,89</t>
+          <t>8,69; 69,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 80,23</t>
+          <t>17,24; 80,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 51,54</t>
+          <t>14,6; 52,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,48; 54,6</t>
+          <t>20,95; 55,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 54,26</t>
+          <t>6,45; 52,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 50,99</t>
+          <t>11,46; 51,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,91; 100,0</t>
+          <t>29,08; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,76</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,78; 63,28</t>
+          <t>21,05; 63,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,12; 47,35</t>
+          <t>14,85; 50,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,0</t>
+          <t>0,0; 25,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 37,34</t>
+          <t>6,14; 36,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 7,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 83,11</t>
+          <t>22,35; 88,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 86,35</t>
+          <t>14,14; 86,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 38,31</t>
+          <t>9,33; 36,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 43,84</t>
+          <t>13,38; 42,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 25,47</t>
+          <t>2,9; 26,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 34,85</t>
+          <t>12,38; 33,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 49,85</t>
+          <t>6,67; 49,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 41,15</t>
+          <t>4,21; 39,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 26,83</t>
+          <t>6,09; 25,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 31,57</t>
+          <t>11,81; 30,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,2</t>
+          <t>0,0; 63,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 29,94</t>
+          <t>3,97; 31,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 41,97</t>
+          <t>4,66; 40,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 41,01</t>
+          <t>4,41; 40,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,64</t>
+          <t>0,59; 4,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 36,34</t>
+          <t>8,87; 37,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 28,82</t>
+          <t>7,25; 29,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,67</t>
+          <t>0,56; 3,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,42; 60,25</t>
+          <t>22,65; 58,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,24; 41,46</t>
+          <t>13,36; 40,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,42; 60,25</t>
+          <t>22,65; 58,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,24; 41,46</t>
+          <t>13,36; 40,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,85; 25,34</t>
+          <t>9,48; 25,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,52; 30,01</t>
+          <t>16,79; 30,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,09</t>
+          <t>0,2; 1,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,2; 44,45</t>
+          <t>25,82; 45,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,03; 35,6</t>
+          <t>18,94; 36,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,14; 1,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,71; 31,91</t>
+          <t>19,59; 32,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,8; 29,92</t>
+          <t>19,55; 30,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,91</t>
+          <t>0,23; 1,02</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1835; 11250</t>
+          <t>1985; 11453</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4746; 16150</t>
+          <t>4970; 16707</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1105; 8544</t>
+          <t>1162; 9277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2036; 8896</t>
+          <t>1911; 8973</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4807; 16767</t>
+          <t>4748; 17181</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9025; 22948</t>
+          <t>8804; 23440</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1053; 8806</t>
+          <t>1047; 8563</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3014; 13739</t>
+          <t>3087; 13826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2402; 8308</t>
+          <t>2416; 8308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4240</t>
+          <t>0; 5316</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5345; 15527</t>
+          <t>5165; 15690</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4556; 15275</t>
+          <t>4791; 16223</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1773</t>
         </is>
       </c>
     </row>
@@ -1965,27 +1965,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7029</t>
+          <t>0; 7519</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1832; 10904</t>
+          <t>1793; 10657</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 10324</t>
+          <t>0; 6590</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2014; 9060</t>
+          <t>2436; 9612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1016; 6350</t>
+          <t>1040; 6345</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3501; 15397</t>
+          <t>3751; 14605</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4773; 16029</t>
+          <t>4891; 15608</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7727</t>
+          <t>0; 6864</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1093</t>
         </is>
       </c>
     </row>
@@ -2128,27 +2128,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1068; 9227</t>
+          <t>1049; 9745</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5594; 17198</t>
+          <t>6111; 16565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3830</t>
+          <t>0; 3788</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>982; 7221</t>
+          <t>967; 7225</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1084; 10002</t>
+          <t>1023; 9560</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3093; 13608</t>
+          <t>3089; 12884</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8992; 23254</t>
+          <t>8699; 22468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2799</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5353</t>
+          <t>0; 5400</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>906; 6958</t>
+          <t>923; 7343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3585</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1344; 11302</t>
+          <t>1254; 10893</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1818; 11241</t>
+          <t>1209; 11077</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>592; 5140</t>
+          <t>714; 5357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2411; 12863</t>
+          <t>3141; 13166</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3771; 14600</t>
+          <t>3672; 14981</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1083; 6506</t>
+          <t>1087; 6077</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7167; 19256</t>
+          <t>7237; 18540</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5222; 16354</t>
+          <t>5271; 16112</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7167; 19256</t>
+          <t>7237; 18540</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5222; 16354</t>
+          <t>5271; 16112</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10773; 27710</t>
+          <t>10363; 27833</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26384; 47921</t>
+          <t>26818; 48850</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>633; 8422</t>
+          <t>1142; 8571</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26699; 47104</t>
+          <t>27363; 48655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20717; 40909</t>
+          <t>21765; 42127</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>599; 5226</t>
+          <t>716; 6058</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42433; 68700</t>
+          <t>42190; 70962</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>51618; 82170</t>
+          <t>53676; 83712</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2251; 11255</t>
+          <t>2533; 11021</t>
         </is>
       </c>
     </row>
